--- a/survey_templates/050_faculty_satisfaction_institutional_support_questionnaire--survey_templates.xlsx
+++ b/survey_templates/050_faculty_satisfaction_institutional_support_questionnaire--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'strongly_agree'}</t>
+          <t>strongly agree</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_agree'}</t>
+          <t>somewhat_agree</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_agree'}</t>
+          <t>somewhat agree</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_disagree'}</t>
+          <t>somewhat_disagree</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_disagree'}</t>
+          <t>somewhat disagree</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'strongly_disagree'}</t>
+          <t>strongly disagree</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'good'}</t>
+          <t>good</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'average'}</t>
+          <t>average</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'very_important'}</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'very_important'}</t>
+          <t>very important</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_important'}</t>
+          <t>somewhat_important</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_important'}</t>
+          <t>somewhat important</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'not_important'}</t>
+          <t>not_important</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'not_important'}</t>
+          <t>not important</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'not_at_all'}</t>
+          <t>not at all</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'very_positive'}</t>
+          <t>very_positive</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'very_positive'}</t>
+          <t>very positive</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_positive'}</t>
+          <t>somewhat_positive</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_positive'}</t>
+          <t>somewhat positive</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_negative'}</t>
+          <t>somewhat_negative</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_negative'}</t>
+          <t>somewhat negative</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'very_negative'}</t>
+          <t>very_negative</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'very_negative'}</t>
+          <t>very negative</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'positive'}</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'positive'}</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'negative'}</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'negative'}</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'very_open'}</t>
+          <t>very_open</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'very_open'}</t>
+          <t>very open</t>
         </is>
       </c>
     </row>
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_open'}</t>
+          <t>somewhat_open</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_open'}</t>
+          <t>somewhat open</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_closed'}</t>
+          <t>somewhat_closed</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_closed'}</t>
+          <t>somewhat closed</t>
         </is>
       </c>
     </row>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'very_closed'}</t>
+          <t>very_closed</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'very_closed'}</t>
+          <t>very closed</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'very_supportive'}</t>
+          <t>very_supportive</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'very_supportive'}</t>
+          <t>very supportive</t>
         </is>
       </c>
     </row>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_supportive'}</t>
+          <t>somewhat_supportive</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_supportive'}</t>
+          <t>somewhat supportive</t>
         </is>
       </c>
     </row>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_unsupportive'}</t>
+          <t>somewhat_unsupportive</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_unsupportive'}</t>
+          <t>somewhat unsupportive</t>
         </is>
       </c>
     </row>
@@ -1365,12 +1365,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'very_unsupportive'}</t>
+          <t>very_unsupportive</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'very_unsupportive'}</t>
+          <t>very unsupportive</t>
         </is>
       </c>
     </row>
@@ -1382,12 +1382,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'very_supportive'}</t>
+          <t>very_supportive</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'very_supportive'}</t>
+          <t>very supportive</t>
         </is>
       </c>
     </row>
@@ -1399,12 +1399,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_supportive'}</t>
+          <t>somewhat_supportive</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_supportive'}</t>
+          <t>somewhat supportive</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1433,12 +1433,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_unsupportive'}</t>
+          <t>somewhat_unsupportive</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_unsupportive'}</t>
+          <t>somewhat unsupportive</t>
         </is>
       </c>
     </row>
@@ -1450,12 +1450,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_'very_unsupportive'}</t>
+          <t>very_unsupportive</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': 'very_unsupportive'}</t>
+          <t>very unsupportive</t>
         </is>
       </c>
     </row>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'value':_'very_supportive'}</t>
+          <t>very_supportive</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'value': 'very_supportive'}</t>
+          <t>very supportive</t>
         </is>
       </c>
     </row>
@@ -1484,12 +1484,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_supportive'}</t>
+          <t>somewhat_supportive</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_supportive'}</t>
+          <t>somewhat supportive</t>
         </is>
       </c>
     </row>
@@ -1501,12 +1501,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'value': 'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1518,12 +1518,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_unsupportive'}</t>
+          <t>somewhat_unsupportive</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_unsupportive'}</t>
+          <t>somewhat unsupportive</t>
         </is>
       </c>
     </row>
@@ -1535,12 +1535,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'value':_'very_unsupportive'}</t>
+          <t>very_unsupportive</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'value': 'very_unsupportive'}</t>
+          <t>very unsupportive</t>
         </is>
       </c>
     </row>
@@ -1552,12 +1552,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'value':_'very_supportive'}</t>
+          <t>very_supportive</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'value': 'very_supportive'}</t>
+          <t>very supportive</t>
         </is>
       </c>
     </row>
@@ -1569,12 +1569,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_supportive'}</t>
+          <t>somewhat_supportive</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_supportive'}</t>
+          <t>somewhat supportive</t>
         </is>
       </c>
     </row>
@@ -1586,12 +1586,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'value': 'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1603,12 +1603,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_unsupportive'}</t>
+          <t>somewhat_unsupportive</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_unsupportive'}</t>
+          <t>somewhat unsupportive</t>
         </is>
       </c>
     </row>
@@ -1620,12 +1620,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'value':_'very_unsupportive'}</t>
+          <t>very_unsupportive</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'value': 'very_unsupportive'}</t>
+          <t>very unsupportive</t>
         </is>
       </c>
     </row>
